--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1490,6 +1490,450 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120288270</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vassbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>371704</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6867309</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120288268</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vassbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>371790</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6867103</v>
+      </c>
+      <c r="S10" t="n">
+        <v>23</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120288255</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vassbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>371815</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6867286</v>
+      </c>
+      <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120288269</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vassbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>371780</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6867297</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -1492,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288270</v>
+        <v>120288268</v>
       </c>
       <c r="B9" t="n">
-        <v>100188</v>
+        <v>100211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371704</v>
+        <v>371790</v>
       </c>
       <c r="R9" t="n">
-        <v>6867309</v>
+        <v>6867103</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288268</v>
+        <v>120288255</v>
       </c>
       <c r="B10" t="n">
-        <v>100188</v>
+        <v>100211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371790</v>
+        <v>371815</v>
       </c>
       <c r="R10" t="n">
-        <v>6867103</v>
+        <v>6867286</v>
       </c>
       <c r="S10" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288255</v>
+        <v>120288269</v>
       </c>
       <c r="B11" t="n">
-        <v>100188</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,25 +1726,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1853</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>371815</v>
+        <v>371780</v>
       </c>
       <c r="R11" t="n">
-        <v>6867286</v>
+        <v>6867297</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288269</v>
+        <v>120288270</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>100211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371780</v>
+        <v>371704</v>
       </c>
       <c r="R12" t="n">
-        <v>6867297</v>
+        <v>6867309</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288268</v>
+        <v>120288270</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371790</v>
+        <v>371704</v>
       </c>
       <c r="R9" t="n">
-        <v>6867103</v>
+        <v>6867309</v>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288255</v>
+        <v>120288269</v>
       </c>
       <c r="B10" t="n">
-        <v>100211</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1853</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371815</v>
+        <v>371780</v>
       </c>
       <c r="R10" t="n">
-        <v>6867286</v>
+        <v>6867297</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288269</v>
+        <v>120288255</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>100211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,25 +1726,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>371780</v>
+        <v>371815</v>
       </c>
       <c r="R11" t="n">
-        <v>6867297</v>
+        <v>6867286</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288270</v>
+        <v>120288268</v>
       </c>
       <c r="B12" t="n">
         <v>100211</v>
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371704</v>
+        <v>371790</v>
       </c>
       <c r="R12" t="n">
-        <v>6867309</v>
+        <v>6867103</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288270</v>
+        <v>120288268</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371704</v>
+        <v>371790</v>
       </c>
       <c r="R9" t="n">
-        <v>6867309</v>
+        <v>6867103</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288269</v>
+        <v>120288270</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>100211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371780</v>
+        <v>371704</v>
       </c>
       <c r="R10" t="n">
-        <v>6867297</v>
+        <v>6867309</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288255</v>
+        <v>120288269</v>
       </c>
       <c r="B11" t="n">
-        <v>100211</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,25 +1726,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1853</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>371815</v>
+        <v>371780</v>
       </c>
       <c r="R11" t="n">
-        <v>6867286</v>
+        <v>6867297</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288268</v>
+        <v>120288255</v>
       </c>
       <c r="B12" t="n">
         <v>100211</v>
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371790</v>
+        <v>371815</v>
       </c>
       <c r="R12" t="n">
-        <v>6867103</v>
+        <v>6867286</v>
       </c>
       <c r="S12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288268</v>
+        <v>120288270</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371790</v>
+        <v>371704</v>
       </c>
       <c r="R9" t="n">
-        <v>6867103</v>
+        <v>6867309</v>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288270</v>
+        <v>120288255</v>
       </c>
       <c r="B10" t="n">
         <v>100211</v>
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371704</v>
+        <v>371815</v>
       </c>
       <c r="R10" t="n">
-        <v>6867309</v>
+        <v>6867286</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288255</v>
+        <v>120288268</v>
       </c>
       <c r="B12" t="n">
         <v>100211</v>
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371815</v>
+        <v>371790</v>
       </c>
       <c r="R12" t="n">
-        <v>6867286</v>
+        <v>6867103</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288270</v>
+        <v>120288255</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371704</v>
+        <v>371815</v>
       </c>
       <c r="R9" t="n">
-        <v>6867309</v>
+        <v>6867286</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288255</v>
+        <v>120288269</v>
       </c>
       <c r="B10" t="n">
-        <v>100211</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1853</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371815</v>
+        <v>371780</v>
       </c>
       <c r="R10" t="n">
-        <v>6867286</v>
+        <v>6867297</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288269</v>
+        <v>120288268</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>100211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,25 +1726,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>371780</v>
+        <v>371790</v>
       </c>
       <c r="R11" t="n">
-        <v>6867297</v>
+        <v>6867103</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288268</v>
+        <v>120288270</v>
       </c>
       <c r="B12" t="n">
         <v>100211</v>
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371790</v>
+        <v>371704</v>
       </c>
       <c r="R12" t="n">
-        <v>6867103</v>
+        <v>6867309</v>
       </c>
       <c r="S12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288255</v>
+        <v>120288270</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371815</v>
+        <v>371704</v>
       </c>
       <c r="R9" t="n">
-        <v>6867286</v>
+        <v>6867309</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288269</v>
+        <v>120288255</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>100211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371780</v>
+        <v>371815</v>
       </c>
       <c r="R10" t="n">
-        <v>6867297</v>
+        <v>6867286</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288270</v>
+        <v>120288269</v>
       </c>
       <c r="B12" t="n">
-        <v>100211</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1853</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371704</v>
+        <v>371780</v>
       </c>
       <c r="R12" t="n">
-        <v>6867309</v>
+        <v>6867297</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288270</v>
+        <v>120288268</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371704</v>
+        <v>371790</v>
       </c>
       <c r="R9" t="n">
-        <v>6867309</v>
+        <v>6867103</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288268</v>
+        <v>120288270</v>
       </c>
       <c r="B11" t="n">
         <v>100211</v>
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>371790</v>
+        <v>371704</v>
       </c>
       <c r="R11" t="n">
-        <v>6867103</v>
+        <v>6867309</v>
       </c>
       <c r="S11" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 21115-2024 artfynd.xlsx
+++ b/artfynd/A 21115-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1714,7 +1714,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288268</v>
+        <v>120288270</v>
       </c>
       <c r="B11" t="n">
         <v>100282</v>
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>371790</v>
+        <v>371704</v>
       </c>
       <c r="R11" t="n">
-        <v>6867103</v>
+        <v>6867309</v>
       </c>
       <c r="S11" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,117 +1822,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>120288270</v>
-      </c>
-      <c r="B12" t="n">
-        <v>100282</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1853</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mosippa</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pulsatilla vernalis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Vassbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>371704</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6867309</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
